--- a/uploads/cloud/1778230441926-393706313.xlsx
+++ b/uploads/cloud/1778230441926-393706313.xlsx
@@ -415,6 +415,12 @@
       <c r="E1" t="str">
         <v/>
       </c>
+      <c r="F1" t="str">
+        <v/>
+      </c>
+      <c r="G1" t="str">
+        <v/>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
@@ -432,6 +438,12 @@
       <c r="E2" t="str">
         <v>備考</v>
       </c>
+      <c r="F2" t="str">
+        <v/>
+      </c>
+      <c r="G2" t="str">
+        <v/>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
@@ -449,6 +461,12 @@
       <c r="E3" t="str">
         <v/>
       </c>
+      <c r="F3" t="str">
+        <v/>
+      </c>
+      <c r="G3" t="str">
+        <v/>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
@@ -466,6 +484,12 @@
       <c r="E4" t="str">
         <v/>
       </c>
+      <c r="F4" t="str">
+        <v/>
+      </c>
+      <c r="G4" t="str">
+        <v/>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
@@ -483,6 +507,12 @@
       <c r="E5" t="str">
         <v>場所分からん</v>
       </c>
+      <c r="F5" t="str">
+        <v/>
+      </c>
+      <c r="G5" t="str">
+        <v/>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
@@ -500,6 +530,12 @@
       <c r="E6" t="str">
         <v/>
       </c>
+      <c r="F6" t="str">
+        <v/>
+      </c>
+      <c r="G6" t="str">
+        <v/>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
@@ -517,6 +553,12 @@
       <c r="E7" t="str">
         <v/>
       </c>
+      <c r="F7" t="str">
+        <v/>
+      </c>
+      <c r="G7" t="str">
+        <v/>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
@@ -534,6 +576,12 @@
       <c r="E8" t="str">
         <v/>
       </c>
+      <c r="F8" t="str">
+        <v/>
+      </c>
+      <c r="G8" t="str">
+        <v/>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
@@ -551,6 +599,12 @@
       <c r="E9" t="str">
         <v/>
       </c>
+      <c r="F9" t="str">
+        <v/>
+      </c>
+      <c r="G9" t="str">
+        <v/>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
@@ -568,6 +622,12 @@
       <c r="E10" t="str">
         <v>フォーム送信ボタン微妙</v>
       </c>
+      <c r="F10" t="str">
+        <v/>
+      </c>
+      <c r="G10" t="str">
+        <v/>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
@@ -585,6 +645,12 @@
       <c r="E11" t="str">
         <v/>
       </c>
+      <c r="F11" t="str">
+        <v/>
+      </c>
+      <c r="G11" t="str">
+        <v/>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
@@ -602,6 +668,12 @@
       <c r="E12" t="str">
         <v/>
       </c>
+      <c r="F12" t="str">
+        <v/>
+      </c>
+      <c r="G12" t="str">
+        <v/>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
@@ -619,6 +691,12 @@
       <c r="E13" t="str">
         <v/>
       </c>
+      <c r="F13" t="str">
+        <v/>
+      </c>
+      <c r="G13" t="str">
+        <v/>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
@@ -636,6 +714,12 @@
       <c r="E14" t="str">
         <v/>
       </c>
+      <c r="F14" t="str">
+        <v/>
+      </c>
+      <c r="G14" t="str">
+        <v/>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
@@ -653,6 +737,12 @@
       <c r="E15" t="str">
         <v>横にスライドしない</v>
       </c>
+      <c r="F15" t="str">
+        <v/>
+      </c>
+      <c r="G15" t="str">
+        <v/>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
@@ -670,6 +760,12 @@
       <c r="E16" t="str">
         <v/>
       </c>
+      <c r="F16" t="str">
+        <v/>
+      </c>
+      <c r="G16" t="str">
+        <v/>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
@@ -687,6 +783,12 @@
       <c r="E17" t="str">
         <v/>
       </c>
+      <c r="F17" t="str">
+        <v/>
+      </c>
+      <c r="G17" t="str">
+        <v/>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
@@ -704,6 +806,12 @@
       <c r="E18" t="str">
         <v/>
       </c>
+      <c r="F18" t="str">
+        <v/>
+      </c>
+      <c r="G18" t="str">
+        <v/>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
@@ -721,6 +829,12 @@
       <c r="E19" t="str">
         <v/>
       </c>
+      <c r="F19" t="str">
+        <v/>
+      </c>
+      <c r="G19" t="str">
+        <v/>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
@@ -738,6 +852,12 @@
       <c r="E20" t="str">
         <v/>
       </c>
+      <c r="F20" t="str">
+        <v/>
+      </c>
+      <c r="G20" t="str">
+        <v/>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
@@ -755,6 +875,12 @@
       <c r="E21" t="str">
         <v/>
       </c>
+      <c r="F21" t="str">
+        <v/>
+      </c>
+      <c r="G21" t="str">
+        <v/>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
@@ -772,6 +898,12 @@
       <c r="E22" t="str">
         <v/>
       </c>
+      <c r="F22" t="str">
+        <v/>
+      </c>
+      <c r="G22" t="str">
+        <v/>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
@@ -789,6 +921,12 @@
       <c r="E23" t="str">
         <v/>
       </c>
+      <c r="F23" t="str">
+        <v/>
+      </c>
+      <c r="G23" t="str">
+        <v/>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
@@ -806,6 +944,12 @@
       <c r="E24" t="str">
         <v/>
       </c>
+      <c r="F24" t="str">
+        <v/>
+      </c>
+      <c r="G24" t="str">
+        <v/>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
@@ -823,6 +967,12 @@
       <c r="E25" t="str">
         <v/>
       </c>
+      <c r="F25" t="str">
+        <v/>
+      </c>
+      <c r="G25" t="str">
+        <v/>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
@@ -840,6 +990,12 @@
       <c r="E26" t="str">
         <v/>
       </c>
+      <c r="F26" t="str">
+        <v/>
+      </c>
+      <c r="G26" t="str">
+        <v/>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
@@ -857,6 +1013,12 @@
       <c r="E27" t="str">
         <v/>
       </c>
+      <c r="F27" t="str">
+        <v/>
+      </c>
+      <c r="G27" t="str">
+        <v/>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
@@ -874,6 +1036,12 @@
       <c r="E28" t="str">
         <v>ヘッダー項目が縦</v>
       </c>
+      <c r="F28" t="str">
+        <v/>
+      </c>
+      <c r="G28" t="str">
+        <v/>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
@@ -891,6 +1059,12 @@
       <c r="E29" t="str">
         <v/>
       </c>
+      <c r="F29" t="str">
+        <v/>
+      </c>
+      <c r="G29" t="str">
+        <v/>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
@@ -908,6 +1082,12 @@
       <c r="E30" t="str">
         <v/>
       </c>
+      <c r="F30" t="str">
+        <v/>
+      </c>
+      <c r="G30" t="str">
+        <v/>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
@@ -925,6 +1105,12 @@
       <c r="E31" t="str">
         <v/>
       </c>
+      <c r="F31" t="str">
+        <v/>
+      </c>
+      <c r="G31" t="str">
+        <v/>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
@@ -942,6 +1128,12 @@
       <c r="E32" t="str">
         <v/>
       </c>
+      <c r="F32" t="str">
+        <v/>
+      </c>
+      <c r="G32" t="str">
+        <v/>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
@@ -959,6 +1151,12 @@
       <c r="E33" t="str">
         <v/>
       </c>
+      <c r="F33" t="str">
+        <v/>
+      </c>
+      <c r="G33" t="str">
+        <v/>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
@@ -976,6 +1174,12 @@
       <c r="E34" t="str">
         <v/>
       </c>
+      <c r="F34" t="str">
+        <v/>
+      </c>
+      <c r="G34" t="str">
+        <v/>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
@@ -993,6 +1197,12 @@
       <c r="E35" t="str">
         <v/>
       </c>
+      <c r="F35" t="str">
+        <v/>
+      </c>
+      <c r="G35" t="str">
+        <v/>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
@@ -1010,6 +1220,12 @@
       <c r="E36" t="str">
         <v/>
       </c>
+      <c r="F36" t="str">
+        <v/>
+      </c>
+      <c r="G36" t="str">
+        <v/>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
@@ -1027,6 +1243,12 @@
       <c r="E37" t="str">
         <v/>
       </c>
+      <c r="F37" t="str">
+        <v/>
+      </c>
+      <c r="G37" t="str">
+        <v/>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
@@ -1044,6 +1266,12 @@
       <c r="E38" t="str">
         <v/>
       </c>
+      <c r="F38" t="str">
+        <v/>
+      </c>
+      <c r="G38" t="str">
+        <v/>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
@@ -1061,6 +1289,12 @@
       <c r="E39" t="str">
         <v/>
       </c>
+      <c r="F39" t="str">
+        <v/>
+      </c>
+      <c r="G39" t="str">
+        <v/>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
@@ -1078,6 +1312,12 @@
       <c r="E40" t="str">
         <v/>
       </c>
+      <c r="F40" t="str">
+        <v/>
+      </c>
+      <c r="G40" t="str">
+        <v/>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
@@ -1095,6 +1335,12 @@
       <c r="E41" t="str">
         <v/>
       </c>
+      <c r="F41" t="str">
+        <v/>
+      </c>
+      <c r="G41" t="str">
+        <v/>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
@@ -1112,6 +1358,12 @@
       <c r="E42" t="str">
         <v/>
       </c>
+      <c r="F42" t="str">
+        <v/>
+      </c>
+      <c r="G42" t="str">
+        <v/>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
@@ -1129,6 +1381,12 @@
       <c r="E43" t="str">
         <v/>
       </c>
+      <c r="F43" t="str">
+        <v/>
+      </c>
+      <c r="G43" t="str">
+        <v/>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
@@ -1146,6 +1404,12 @@
       <c r="E44" t="str">
         <v/>
       </c>
+      <c r="F44" t="str">
+        <v/>
+      </c>
+      <c r="G44" t="str">
+        <v/>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
@@ -1163,6 +1427,12 @@
       <c r="E45" t="str">
         <v/>
       </c>
+      <c r="F45" t="str">
+        <v/>
+      </c>
+      <c r="G45" t="str">
+        <v/>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
@@ -1180,6 +1450,12 @@
       <c r="E46" t="str">
         <v/>
       </c>
+      <c r="F46" t="str">
+        <v/>
+      </c>
+      <c r="G46" t="str">
+        <v/>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
@@ -1197,6 +1473,12 @@
       <c r="E47" t="str">
         <v/>
       </c>
+      <c r="F47" t="str">
+        <v/>
+      </c>
+      <c r="G47" t="str">
+        <v/>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
@@ -1214,6 +1496,12 @@
       <c r="E48" t="str">
         <v/>
       </c>
+      <c r="F48" t="str">
+        <v/>
+      </c>
+      <c r="G48" t="str">
+        <v/>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
@@ -1231,6 +1519,12 @@
       <c r="E49" t="str">
         <v/>
       </c>
+      <c r="F49" t="str">
+        <v/>
+      </c>
+      <c r="G49" t="str">
+        <v/>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
@@ -1248,6 +1542,12 @@
       <c r="E50" t="str">
         <v/>
       </c>
+      <c r="F50" t="str">
+        <v/>
+      </c>
+      <c r="G50" t="str">
+        <v/>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
@@ -1265,6 +1565,12 @@
       <c r="E51" t="str">
         <v/>
       </c>
+      <c r="F51" t="str">
+        <v/>
+      </c>
+      <c r="G51" t="str">
+        <v/>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
@@ -1282,6 +1588,12 @@
       <c r="E52" t="str">
         <v/>
       </c>
+      <c r="F52" t="str">
+        <v/>
+      </c>
+      <c r="G52" t="str">
+        <v/>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
@@ -1299,6 +1611,12 @@
       <c r="E53" t="str">
         <v/>
       </c>
+      <c r="F53" t="str">
+        <v/>
+      </c>
+      <c r="G53" t="str">
+        <v/>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
@@ -1316,6 +1634,12 @@
       <c r="E54" t="str">
         <v/>
       </c>
+      <c r="F54" t="str">
+        <v/>
+      </c>
+      <c r="G54" t="str">
+        <v/>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
@@ -1333,6 +1657,12 @@
       <c r="E55" t="str">
         <v/>
       </c>
+      <c r="F55" t="str">
+        <v/>
+      </c>
+      <c r="G55" t="str">
+        <v/>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
@@ -1350,6 +1680,12 @@
       <c r="E56" t="str">
         <v/>
       </c>
+      <c r="F56" t="str">
+        <v/>
+      </c>
+      <c r="G56" t="str">
+        <v/>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
@@ -1367,6 +1703,12 @@
       <c r="E57" t="str">
         <v/>
       </c>
+      <c r="F57" t="str">
+        <v/>
+      </c>
+      <c r="G57" t="str">
+        <v/>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
@@ -1384,6 +1726,12 @@
       <c r="E58" t="str">
         <v>フォーム送信</v>
       </c>
+      <c r="F58" t="str">
+        <v/>
+      </c>
+      <c r="G58" t="str">
+        <v/>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
@@ -1401,6 +1749,12 @@
       <c r="E59" t="str">
         <v/>
       </c>
+      <c r="F59" t="str">
+        <v/>
+      </c>
+      <c r="G59" t="str">
+        <v/>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
@@ -1418,6 +1772,12 @@
       <c r="E60" t="str">
         <v/>
       </c>
+      <c r="F60" t="str">
+        <v/>
+      </c>
+      <c r="G60" t="str">
+        <v/>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
@@ -1435,6 +1795,12 @@
       <c r="E61" t="str">
         <v/>
       </c>
+      <c r="F61" t="str">
+        <v/>
+      </c>
+      <c r="G61" t="str">
+        <v/>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
@@ -1452,6 +1818,12 @@
       <c r="E62" t="str">
         <v/>
       </c>
+      <c r="F62" t="str">
+        <v/>
+      </c>
+      <c r="G62" t="str">
+        <v/>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
@@ -1469,6 +1841,12 @@
       <c r="E63" t="str">
         <v/>
       </c>
+      <c r="F63" t="str">
+        <v/>
+      </c>
+      <c r="G63" t="str">
+        <v/>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
@@ -1486,6 +1864,12 @@
       <c r="E64" t="str">
         <v>リアクション・コメント含む</v>
       </c>
+      <c r="F64" t="str">
+        <v/>
+      </c>
+      <c r="G64" t="str">
+        <v/>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
@@ -1503,6 +1887,12 @@
       <c r="E65" t="str">
         <v/>
       </c>
+      <c r="F65" t="str">
+        <v/>
+      </c>
+      <c r="G65" t="str">
+        <v/>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
@@ -1520,6 +1910,12 @@
       <c r="E66" t="str">
         <v/>
       </c>
+      <c r="F66" t="str">
+        <v/>
+      </c>
+      <c r="G66" t="str">
+        <v/>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
@@ -1537,6 +1933,12 @@
       <c r="E67" t="str">
         <v/>
       </c>
+      <c r="F67" t="str">
+        <v/>
+      </c>
+      <c r="G67" t="str">
+        <v/>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
@@ -1554,6 +1956,12 @@
       <c r="E68" t="str">
         <v/>
       </c>
+      <c r="F68" t="str">
+        <v/>
+      </c>
+      <c r="G68" t="str">
+        <v/>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
@@ -1571,6 +1979,12 @@
       <c r="E69" t="str">
         <v>ファイル添付含む</v>
       </c>
+      <c r="F69" t="str">
+        <v/>
+      </c>
+      <c r="G69" t="str">
+        <v/>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
@@ -1588,6 +2002,12 @@
       <c r="E70" t="str">
         <v>コメント・いいね含む</v>
       </c>
+      <c r="F70" t="str">
+        <v/>
+      </c>
+      <c r="G70" t="str">
+        <v/>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
@@ -1605,6 +2025,12 @@
       <c r="E71" t="str">
         <v/>
       </c>
+      <c r="F71" t="str">
+        <v/>
+      </c>
+      <c r="G71" t="str">
+        <v/>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
@@ -1622,6 +2048,12 @@
       <c r="E72" t="str">
         <v/>
       </c>
+      <c r="F72" t="str">
+        <v/>
+      </c>
+      <c r="G72" t="str">
+        <v/>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
@@ -1639,6 +2071,12 @@
       <c r="E73" t="str">
         <v/>
       </c>
+      <c r="F73" t="str">
+        <v/>
+      </c>
+      <c r="G73" t="str">
+        <v/>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
@@ -1656,6 +2094,12 @@
       <c r="E74" t="str">
         <v/>
       </c>
+      <c r="F74" t="str">
+        <v/>
+      </c>
+      <c r="G74" t="str">
+        <v/>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
@@ -1673,6 +2117,12 @@
       <c r="E75" t="str">
         <v/>
       </c>
+      <c r="F75" t="str">
+        <v/>
+      </c>
+      <c r="G75" t="str">
+        <v/>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
@@ -1690,6 +2140,12 @@
       <c r="E76" t="str">
         <v>ダウンロード処理</v>
       </c>
+      <c r="F76" t="str">
+        <v/>
+      </c>
+      <c r="G76" t="str">
+        <v/>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
@@ -1707,6 +2163,12 @@
       <c r="E77" t="str">
         <v/>
       </c>
+      <c r="F77" t="str">
+        <v/>
+      </c>
+      <c r="G77" t="str">
+        <v/>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
@@ -1724,6 +2186,12 @@
       <c r="E78" t="str">
         <v/>
       </c>
+      <c r="F78" t="str">
+        <v/>
+      </c>
+      <c r="G78" t="str">
+        <v/>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
@@ -1741,6 +2209,12 @@
       <c r="E79" t="str">
         <v>ファイルアップロード含む</v>
       </c>
+      <c r="F79" t="str">
+        <v/>
+      </c>
+      <c r="G79" t="str">
+        <v/>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
@@ -1758,6 +2232,12 @@
       <c r="E80" t="str">
         <v/>
       </c>
+      <c r="F80" t="str">
+        <v/>
+      </c>
+      <c r="G80" t="str">
+        <v/>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
@@ -1775,6 +2255,12 @@
       <c r="E81" t="str">
         <v/>
       </c>
+      <c r="F81" t="str">
+        <v/>
+      </c>
+      <c r="G81" t="str">
+        <v/>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
@@ -1792,6 +2278,12 @@
       <c r="E82" t="str">
         <v>ログイン不要</v>
       </c>
+      <c r="F82" t="str">
+        <v/>
+      </c>
+      <c r="G82" t="str">
+        <v/>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
@@ -1809,6 +2301,12 @@
       <c r="E83" t="str">
         <v>ログイン不要</v>
       </c>
+      <c r="F83" t="str">
+        <v/>
+      </c>
+      <c r="G83" t="str">
+        <v/>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
@@ -1826,6 +2324,12 @@
       <c r="E84" t="str">
         <v/>
       </c>
+      <c r="F84" t="str">
+        <v/>
+      </c>
+      <c r="G84" t="str">
+        <v/>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
@@ -1843,6 +2347,12 @@
       <c r="E85" t="str">
         <v/>
       </c>
+      <c r="F85" t="str">
+        <v/>
+      </c>
+      <c r="G85" t="str">
+        <v/>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
@@ -1860,6 +2370,12 @@
       <c r="E86" t="str">
         <v/>
       </c>
+      <c r="F86" t="str">
+        <v/>
+      </c>
+      <c r="G86" t="str">
+        <v/>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
@@ -1877,6 +2393,12 @@
       <c r="E87" t="str">
         <v/>
       </c>
+      <c r="F87" t="str">
+        <v/>
+      </c>
+      <c r="G87" t="str">
+        <v/>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
@@ -1894,6 +2416,12 @@
       <c r="E88" t="str">
         <v/>
       </c>
+      <c r="F88" t="str">
+        <v/>
+      </c>
+      <c r="G88" t="str">
+        <v/>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
@@ -1911,6 +2439,12 @@
       <c r="E89" t="str">
         <v>チャットが長くなると見つけられなくなる</v>
       </c>
+      <c r="F89" t="str">
+        <v/>
+      </c>
+      <c r="G89" t="str">
+        <v/>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
@@ -1928,6 +2462,12 @@
       <c r="E90" t="str">
         <v>ぐちゃぐちゃ</v>
       </c>
+      <c r="F90" t="str">
+        <v/>
+      </c>
+      <c r="G90" t="str">
+        <v/>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
@@ -1945,6 +2485,12 @@
       <c r="E91" t="str">
         <v>上記同様</v>
       </c>
+      <c r="F91" t="str">
+        <v/>
+      </c>
+      <c r="G91" t="str">
+        <v/>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
@@ -1962,6 +2508,12 @@
       <c r="E92" t="str">
         <v>どこ</v>
       </c>
+      <c r="F92" t="str">
+        <v/>
+      </c>
+      <c r="G92" t="str">
+        <v/>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
@@ -1979,6 +2531,12 @@
       <c r="E93" t="str">
         <v/>
       </c>
+      <c r="F93" t="str">
+        <v/>
+      </c>
+      <c r="G93" t="str">
+        <v/>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
@@ -1996,6 +2554,12 @@
       <c r="E94" t="str">
         <v/>
       </c>
+      <c r="F94" t="str">
+        <v/>
+      </c>
+      <c r="G94" t="str">
+        <v/>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
@@ -2013,6 +2577,12 @@
       <c r="E95" t="str">
         <v/>
       </c>
+      <c r="F95" t="str">
+        <v/>
+      </c>
+      <c r="G95" t="str">
+        <v/>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
@@ -2030,6 +2600,12 @@
       <c r="E96" t="str">
         <v/>
       </c>
+      <c r="F96" t="str">
+        <v/>
+      </c>
+      <c r="G96" t="str">
+        <v/>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
@@ -2047,6 +2623,12 @@
       <c r="E97" t="str">
         <v/>
       </c>
+      <c r="F97" t="str">
+        <v/>
+      </c>
+      <c r="G97" t="str">
+        <v/>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
@@ -2064,6 +2646,12 @@
       <c r="E98" t="str">
         <v/>
       </c>
+      <c r="F98" t="str">
+        <v/>
+      </c>
+      <c r="G98" t="str">
+        <v/>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
@@ -2081,6 +2669,12 @@
       <c r="E99" t="str">
         <v/>
       </c>
+      <c r="F99" t="str">
+        <v/>
+      </c>
+      <c r="G99" t="str">
+        <v/>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
@@ -2098,6 +2692,12 @@
       <c r="E100" t="str">
         <v/>
       </c>
+      <c r="F100" t="str">
+        <v/>
+      </c>
+      <c r="G100" t="str">
+        <v/>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
@@ -2115,6 +2715,12 @@
       <c r="E101" t="str">
         <v/>
       </c>
+      <c r="F101" t="str">
+        <v/>
+      </c>
+      <c r="G101" t="str">
+        <v/>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="str">
@@ -2132,6 +2738,12 @@
       <c r="E102" t="str">
         <v/>
       </c>
+      <c r="F102" t="str">
+        <v/>
+      </c>
+      <c r="G102" t="str">
+        <v/>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="str">
@@ -2149,6 +2761,12 @@
       <c r="E103" t="str">
         <v/>
       </c>
+      <c r="F103" t="str">
+        <v/>
+      </c>
+      <c r="G103" t="str">
+        <v/>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="str">
@@ -2166,6 +2784,12 @@
       <c r="E104" t="str">
         <v/>
       </c>
+      <c r="F104" t="str">
+        <v/>
+      </c>
+      <c r="G104" t="str">
+        <v/>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="str">
@@ -2183,6 +2807,12 @@
       <c r="E105" t="str">
         <v/>
       </c>
+      <c r="F105" t="str">
+        <v/>
+      </c>
+      <c r="G105" t="str">
+        <v/>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="str">
@@ -2200,6 +2830,12 @@
       <c r="E106" t="str">
         <v/>
       </c>
+      <c r="F106" t="str">
+        <v/>
+      </c>
+      <c r="G106" t="str">
+        <v/>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="str">
@@ -2217,6 +2853,12 @@
       <c r="E107" t="str">
         <v/>
       </c>
+      <c r="F107" t="str">
+        <v/>
+      </c>
+      <c r="G107" t="str">
+        <v/>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="str">
@@ -2234,6 +2876,12 @@
       <c r="E108" t="str">
         <v/>
       </c>
+      <c r="F108" t="str">
+        <v/>
+      </c>
+      <c r="G108" t="str">
+        <v/>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="str">
@@ -2251,6 +2899,12 @@
       <c r="E109" t="str">
         <v/>
       </c>
+      <c r="F109" t="str">
+        <v/>
+      </c>
+      <c r="G109" t="str">
+        <v/>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="str">
@@ -2268,6 +2922,12 @@
       <c r="E110" t="str">
         <v/>
       </c>
+      <c r="F110" t="str">
+        <v/>
+      </c>
+      <c r="G110" t="str">
+        <v/>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="str">
@@ -2285,6 +2945,12 @@
       <c r="E111" t="str">
         <v/>
       </c>
+      <c r="F111" t="str">
+        <v/>
+      </c>
+      <c r="G111" t="str">
+        <v/>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="str">
@@ -2302,6 +2968,12 @@
       <c r="E112" t="str">
         <v/>
       </c>
+      <c r="F112" t="str">
+        <v/>
+      </c>
+      <c r="G112" t="str">
+        <v/>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
@@ -2318,6 +2990,127 @@
       </c>
       <c r="E113" t="str">
         <v>全ページ共通ウィジェット</v>
+      </c>
+      <c r="F113" t="str">
+        <v/>
+      </c>
+      <c r="G113" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="str">
+        <v/>
+      </c>
+      <c r="B114" t="str">
+        <v/>
+      </c>
+      <c r="C114" t="str">
+        <v/>
+      </c>
+      <c r="D114" t="str">
+        <v/>
+      </c>
+      <c r="E114" t="str">
+        <v/>
+      </c>
+      <c r="F114" t="str">
+        <v/>
+      </c>
+      <c r="G114" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="str">
+        <v/>
+      </c>
+      <c r="B115" t="str">
+        <v/>
+      </c>
+      <c r="C115" t="str">
+        <v/>
+      </c>
+      <c r="D115" t="str">
+        <v/>
+      </c>
+      <c r="E115" t="str">
+        <v/>
+      </c>
+      <c r="F115" t="str">
+        <v/>
+      </c>
+      <c r="G115" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="str">
+        <v/>
+      </c>
+      <c r="B116" t="str">
+        <v/>
+      </c>
+      <c r="C116" t="str">
+        <v/>
+      </c>
+      <c r="D116" t="str">
+        <v/>
+      </c>
+      <c r="E116" t="str">
+        <v/>
+      </c>
+      <c r="F116" t="str">
+        <v/>
+      </c>
+      <c r="G116" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="str">
+        <v/>
+      </c>
+      <c r="B117" t="str">
+        <v/>
+      </c>
+      <c r="C117" t="str">
+        <v/>
+      </c>
+      <c r="D117" t="str">
+        <v/>
+      </c>
+      <c r="E117" t="str">
+        <v/>
+      </c>
+      <c r="F117" t="str">
+        <v/>
+      </c>
+      <c r="G117" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="str">
+        <v/>
+      </c>
+      <c r="B118" t="str">
+        <v/>
+      </c>
+      <c r="C118" t="str">
+        <v/>
+      </c>
+      <c r="D118" t="str">
+        <v/>
+      </c>
+      <c r="E118" t="str">
+        <v/>
+      </c>
+      <c r="F118" t="str">
+        <v/>
+      </c>
+      <c r="G118" t="str">
+        <v/>
       </c>
     </row>
   </sheetData>
